--- a/assets/constructions/examples/ctd_mie_chamf.xlsx
+++ b/assets/constructions/examples/ctd_mie_chamf.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB6"/>
+  <dimension ref="A1:AF6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -569,6 +569,26 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -578,50 +598,50 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TP45-C20-20-120-1T</t>
+          <t>TP30-C32-55-160-3T</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TP45</t>
+          <t>TP30</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.4</v>
+        <v>54.5</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="F2" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="G2" t="n">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>0.27</v>
+        <v>0.98</v>
       </c>
       <c r="N2" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="O2" t="b">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>8.199999999999999</v>
+        <v>9.25</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>TPMN1603</t>
+          <t>TPMN2204</t>
         </is>
       </c>
       <c r="R2" t="n">
@@ -629,12 +649,12 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>HA-20</t>
+          <t>HA-32</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>ISO_TP1603W</t>
+          <t>ISO_TP2204W</t>
         </is>
       </c>
       <c r="U2" t="n">
@@ -656,7 +676,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>TP1603_H</t>
+          <t>TP2204_H</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr"/>
@@ -664,6 +684,20 @@
         <is>
           <t>2019 / DEREK</t>
         </is>
+      </c>
+      <c r="AC2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>89.75</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>7357.16</v>
       </c>
     </row>
     <row r="3">
@@ -759,37 +793,43 @@
           <t>2022/LIKON Инструментальный каталог</t>
         </is>
       </c>
+      <c r="AC3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LIKON</t>
+          <t>WIDIA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>STGF45-14-35-20-2</t>
+          <t>12292550800</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>STGF</t>
+          <t>M25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>35</v>
+        <v>37.8</v>
       </c>
       <c r="E4" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G4" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H4" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="I4" t="n">
         <v>2</v>
@@ -799,17 +839,21 @@
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="n">
+        <v>0.7</v>
+      </c>
       <c r="N4" t="n">
         <v>45</v>
       </c>
-      <c r="O4" t="inlineStr"/>
+      <c r="O4" t="b">
+        <v>0</v>
+      </c>
       <c r="P4" t="n">
-        <v>11.3</v>
+        <v>6.4</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>TCMT16T3</t>
+          <t>SD..0903..</t>
         </is>
       </c>
       <c r="R4" t="n">
@@ -817,19 +861,19 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>HB-20</t>
+          <t>HA-25</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>LIKON_TC16T3H</t>
+          <t>WIDIA_SD0903H</t>
         </is>
       </c>
       <c r="U4" t="n">
         <v>1</v>
       </c>
       <c r="V4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
@@ -839,20 +883,30 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>HA</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>LIK_TC16T3H</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr"/>
+          <t>WID_SD0903_H</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>WID_SD0903_X5</t>
+        </is>
+      </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2022/LIKON Инструментальный каталог</t>
-        </is>
-      </c>
+          <t>2019 /Novo</t>
+        </is>
+      </c>
+      <c r="AC4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -862,19 +916,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TP60-C25-40-120-2T</t>
+          <t>TP30-C25-40-120-2T</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TP60</t>
+          <t>TP30</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.7</v>
+        <v>39</v>
       </c>
       <c r="E5" t="n">
-        <v>15.8</v>
+        <v>26</v>
       </c>
       <c r="F5" t="n">
         <v>25</v>
@@ -892,16 +946,16 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
       <c r="N5" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="O5" t="b">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>10.95</v>
+        <v>6.5</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -948,54 +1002,76 @@
         <is>
           <t>2019 / DEREK</t>
         </is>
+      </c>
+      <c r="AC5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>79.06</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
+        <v>6480.86</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LIKON</t>
+          <t>DEREK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SDGF55-D63-25-40-120-4</t>
+          <t>SSP-C20-20-130-1T</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SDGF</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>SSP</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>20</v>
+      </c>
       <c r="E6" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G6" t="n">
-        <v>120</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
+        <v>130</v>
+      </c>
+      <c r="H6" t="n">
+        <v>20</v>
+      </c>
       <c r="I6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>0.28</v>
+      </c>
       <c r="N6" t="n">
-        <v>55</v>
-      </c>
-      <c r="O6" t="inlineStr"/>
+        <v>45</v>
+      </c>
+      <c r="O6" t="b">
+        <v>0</v>
+      </c>
       <c r="P6" t="n">
-        <v>9.800000000000001</v>
+        <v>11.3</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>DCMT11T3</t>
+          <t>TCMX16T308</t>
         </is>
       </c>
       <c r="R6" t="n">
@@ -1003,19 +1079,19 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>HA-25</t>
+          <t>HA-20</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>ISO_DC11T3H</t>
+          <t>ISO_TC16T3H</t>
         </is>
       </c>
       <c r="U6" t="n">
         <v>1</v>
       </c>
       <c r="V6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
@@ -1030,14 +1106,28 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>DC11T3H</t>
+          <t>TC16T3_H</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2022/LIKON Инструментальный каталог</t>
-        </is>
+          <t>2019 / DEREK</t>
+        </is>
+      </c>
+      <c r="AC6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>115.4</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>9459.790000000001</v>
       </c>
     </row>
   </sheetData>
